--- a/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.796592235565186</v>
+        <v>2.967935562133789</v>
       </c>
       <c r="E2" t="n">
         <v>0.9995308080898969</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5.286661624908447</v>
+        <v>5.25422739982605</v>
       </c>
       <c r="E3" t="n">
         <v>0.9996176561182242</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.796592235565186</v>
+        <v>2.967935562133789</v>
       </c>
       <c r="E2" t="n">
         <v>0.9995308080898969</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5.286661624908447</v>
+        <v>5.25422739982605</v>
       </c>
       <c r="E3" t="n">
         <v>0.9996176561182242</v>

--- a/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.967935562133789</v>
+        <v>3.090390920639038</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9995308080898969</v>
+        <v>0.9964407905175324</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9996614248307802</v>
+        <v>0.9981552400435884</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3626074032427155</v>
+        <v>0.846406609551614</v>
       </c>
       <c r="H2" t="n">
-        <v>0.217531223646855</v>
+        <v>0.5817881338169909</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 3, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5.25422739982605</v>
+        <v>4.720860719680786</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9996176561182242</v>
+        <v>0.9975889547112533</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9997514131726544</v>
+        <v>0.9981552400435884</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3107049486552608</v>
+        <v>0.846406609551614</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2144502144103884</v>
+        <v>0.5817881338169909</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 3, 'min_samples_split': 10, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.967935562133789</v>
+        <v>3.090390920639038</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9995308080898969</v>
+        <v>0.9964407905175324</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9996614248307802</v>
+        <v>0.9981552400435884</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3626074032427155</v>
+        <v>0.846406609551614</v>
       </c>
       <c r="H2" t="n">
-        <v>0.217531223646855</v>
+        <v>0.5817881338169909</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 3, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5.25422739982605</v>
+        <v>4.720860719680786</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9996176561182242</v>
+        <v>0.9975889547112533</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9997514131726544</v>
+        <v>0.9981552400435884</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3107049486552608</v>
+        <v>0.846406609551614</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2144502144103884</v>
+        <v>0.5817881338169909</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 3, 'min_samples_split': 10, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.090390920639038</v>
+        <v>81.58771443367004</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9964407905175324</v>
+        <v>0.9539223716965667</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9981552400435884</v>
+        <v>0.9609852594920165</v>
       </c>
       <c r="G2" t="n">
-        <v>0.846406609551614</v>
+        <v>35.14851072763138</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5817881338169909</v>
+        <v>21.2876999547741</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>4.720860719680786</v>
+        <v>146.5513699054718</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9975889547112533</v>
+        <v>0.9584973729158508</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9981552400435884</v>
+        <v>0.961249210520087</v>
       </c>
       <c r="G3" t="n">
-        <v>0.846406609551614</v>
+        <v>35.02941176345791</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5817881338169909</v>
+        <v>21.47659480565336</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_samples_split': 10, 'n_estimators': 200}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>311.200599193573</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9601119802197129</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9628617064749472</v>
+      </c>
+      <c r="G4" t="n">
+        <v>34.2928467877029</v>
+      </c>
+      <c r="H4" t="n">
+        <v>21.36115234734118</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.090390920639038</v>
+        <v>81.58771443367004</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9964407905175324</v>
+        <v>0.9539223716965667</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9981552400435884</v>
+        <v>0.9609852594920165</v>
       </c>
       <c r="G2" t="n">
-        <v>0.846406609551614</v>
+        <v>35.14851072763138</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5817881338169909</v>
+        <v>21.2876999547741</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>4.720860719680786</v>
+        <v>146.5513699054718</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9975889547112533</v>
+        <v>0.9584973729158508</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9981552400435884</v>
+        <v>0.961249210520087</v>
       </c>
       <c r="G3" t="n">
-        <v>0.846406609551614</v>
+        <v>35.02941176345791</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5817881338169909</v>
+        <v>21.47659480565336</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_samples_split': 10, 'n_estimators': 200}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>311.200599193573</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9601119802197129</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9628617064749472</v>
+      </c>
+      <c r="G4" t="n">
+        <v>34.2928467877029</v>
+      </c>
+      <c r="H4" t="n">
+        <v>21.36115234734118</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>81.58771443367004</v>
+        <v>276.8292608261108</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9539223716965667</v>
+        <v>0.9602943270145412</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9609852594920165</v>
+        <v>0.9621496998976331</v>
       </c>
       <c r="G2" t="n">
-        <v>35.14851072763138</v>
+        <v>34.62001331527443</v>
       </c>
       <c r="H2" t="n">
-        <v>21.2876999547741</v>
+        <v>21.29884542120722</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'min_samples_split': 5, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -523,61 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>146.5513699054718</v>
+        <v>354.9995188713074</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9584973729158508</v>
+        <v>0.9607920144022914</v>
       </c>
       <c r="F3" t="n">
-        <v>0.961249210520087</v>
+        <v>0.9609852594920165</v>
       </c>
       <c r="G3" t="n">
-        <v>35.02941176345791</v>
+        <v>35.14851072763138</v>
       </c>
       <c r="H3" t="n">
-        <v>21.47659480565336</v>
+        <v>21.2876999547741</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_samples_split': 10, 'n_estimators': 200}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>GradientBoosting</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>311.200599193573</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9601119802197129</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9628617064749472</v>
-      </c>
-      <c r="G4" t="n">
-        <v>34.2928467877029</v>
-      </c>
-      <c r="H4" t="n">
-        <v>21.36115234734118</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>81.58771443367004</v>
+        <v>276.8292608261108</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9539223716965667</v>
+        <v>0.9602943270145412</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9609852594920165</v>
+        <v>0.9621496998976331</v>
       </c>
       <c r="G2" t="n">
-        <v>35.14851072763138</v>
+        <v>34.62001331527443</v>
       </c>
       <c r="H2" t="n">
-        <v>21.2876999547741</v>
+        <v>21.29884542120722</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'min_samples_split': 5, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -689,61 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>146.5513699054718</v>
+        <v>354.9995188713074</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9584973729158508</v>
+        <v>0.9607920144022914</v>
       </c>
       <c r="F3" t="n">
-        <v>0.961249210520087</v>
+        <v>0.9609852594920165</v>
       </c>
       <c r="G3" t="n">
-        <v>35.02941176345791</v>
+        <v>35.14851072763138</v>
       </c>
       <c r="H3" t="n">
-        <v>21.47659480565336</v>
+        <v>21.2876999547741</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_samples_split': 10, 'n_estimators': 200}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>GradientBoosting</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>311.200599193573</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9601119802197129</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9628617064749472</v>
-      </c>
-      <c r="G4" t="n">
-        <v>34.2928467877029</v>
-      </c>
-      <c r="H4" t="n">
-        <v>21.36115234734118</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>276.8292608261108</v>
+        <v>1.929407596588135</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9602943270145412</v>
+        <v>0.9964407905175324</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9621496998976331</v>
+        <v>0.9981552400435884</v>
       </c>
       <c r="G2" t="n">
-        <v>34.62001331527443</v>
+        <v>0.846406609551614</v>
       </c>
       <c r="H2" t="n">
-        <v>21.29884542120722</v>
+        <v>0.5817881338169909</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'min_samples_split': 5, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -523,26 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>354.9995188713074</v>
+        <v>3.156977415084839</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9607920144022914</v>
+        <v>0.9975889547112533</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9609852594920165</v>
+        <v>0.9981552400435884</v>
       </c>
       <c r="G3" t="n">
-        <v>35.14851072763138</v>
+        <v>0.846406609551614</v>
       </c>
       <c r="H3" t="n">
-        <v>21.2876999547741</v>
+        <v>0.5817881338169909</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -619,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>276.8292608261108</v>
+        <v>1.929407596588135</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9602943270145412</v>
+        <v>0.9964407905175324</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9621496998976331</v>
+        <v>0.9981552400435884</v>
       </c>
       <c r="G2" t="n">
-        <v>34.62001331527443</v>
+        <v>0.846406609551614</v>
       </c>
       <c r="H2" t="n">
-        <v>21.29884542120722</v>
+        <v>0.5817881338169909</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'min_samples_split': 5, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -654,26 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>354.9995188713074</v>
+        <v>3.156977415084839</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9607920144022914</v>
+        <v>0.9975889547112533</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9609852594920165</v>
+        <v>0.9981552400435884</v>
       </c>
       <c r="G3" t="n">
-        <v>35.14851072763138</v>
+        <v>0.846406609551614</v>
       </c>
       <c r="H3" t="n">
-        <v>21.2876999547741</v>
+        <v>0.5817881338169909</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.929407596588135</v>
+        <v>5.12074613571167</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9964407905175324</v>
+        <v>0.996443640964655</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9981552400435884</v>
+        <v>0.9983193555080503</v>
       </c>
       <c r="G2" t="n">
-        <v>0.846406609551614</v>
+        <v>0.8078803460989455</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5817881338169909</v>
+        <v>0.5601970096148988</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.156977415084839</v>
+        <v>9.203692674636841</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9975889547112533</v>
+        <v>0.9976168879730635</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9981552400435884</v>
+        <v>0.9983193555080503</v>
       </c>
       <c r="G3" t="n">
-        <v>0.846406609551614</v>
+        <v>0.8078803460989455</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5817881338169909</v>
+        <v>0.5601970096148988</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.929407596588135</v>
+        <v>5.12074613571167</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9964407905175324</v>
+        <v>0.996443640964655</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9981552400435884</v>
+        <v>0.9983193555080503</v>
       </c>
       <c r="G2" t="n">
-        <v>0.846406609551614</v>
+        <v>0.8078803460989455</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5817881338169909</v>
+        <v>0.5601970096148988</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.156977415084839</v>
+        <v>9.203692674636841</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9975889547112533</v>
+        <v>0.9976168879730635</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9981552400435884</v>
+        <v>0.9983193555080503</v>
       </c>
       <c r="G3" t="n">
-        <v>0.846406609551614</v>
+        <v>0.8078803460989455</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5817881338169909</v>
+        <v>0.5601970096148988</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
@@ -491,10 +491,10 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.12074613571167</v>
+        <v>5.103028297424316</v>
       </c>
       <c r="E2" t="n">
-        <v>0.996443640964655</v>
+        <v>0.9964444112983152</v>
       </c>
       <c r="F2" t="n">
         <v>0.9983193555080503</v>
@@ -526,10 +526,10 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>9.203692674636841</v>
+        <v>9.120049715042114</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9976168879730635</v>
+        <v>0.9976341993814136</v>
       </c>
       <c r="F3" t="n">
         <v>0.9983193555080503</v>
@@ -622,10 +622,10 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.12074613571167</v>
+        <v>5.103028297424316</v>
       </c>
       <c r="E2" t="n">
-        <v>0.996443640964655</v>
+        <v>0.9964444112983152</v>
       </c>
       <c r="F2" t="n">
         <v>0.9983193555080503</v>
@@ -657,10 +657,10 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>9.203692674636841</v>
+        <v>9.120049715042114</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9976168879730635</v>
+        <v>0.9976341993814136</v>
       </c>
       <c r="F3" t="n">
         <v>0.9983193555080503</v>

--- a/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.103028297424316</v>
+        <v>0.4317066669464111</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9964444112983152</v>
+        <v>0.9962821294270688</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9983193555080503</v>
+        <v>0.9978246390639918</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8078803460989455</v>
+        <v>0.9191254197681974</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5601970096148988</v>
+        <v>0.6382677938619158</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 250}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>9.120049715042114</v>
+        <v>0.8725149631500244</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9976341993814136</v>
+        <v>0.9974229884587255</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9983193555080503</v>
+        <v>0.9971987634537949</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8078803460989455</v>
+        <v>1.042999274810321</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5601970096148988</v>
+        <v>0.634718037848133</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 250}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.103028297424316</v>
+        <v>0.4317066669464111</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9964444112983152</v>
+        <v>0.9962821294270688</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9983193555080503</v>
+        <v>0.9978246390639918</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8078803460989455</v>
+        <v>0.9191254197681974</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5601970096148988</v>
+        <v>0.6382677938619158</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 250}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>9.120049715042114</v>
+        <v>0.8725149631500244</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9976341993814136</v>
+        <v>0.9974229884587255</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9983193555080503</v>
+        <v>0.9971987634537949</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8078803460989455</v>
+        <v>1.042999274810321</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5601970096148988</v>
+        <v>0.634718037848133</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 250}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4317066669464111</v>
+        <v>75.22472238540649</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9962821294270688</v>
+        <v>0.9516741927489486</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9978246390639918</v>
+        <v>0.9579448551240813</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9191254197681974</v>
+        <v>36.49237538596583</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6382677938619158</v>
+        <v>22.45833191275022</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 5, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8725149631500244</v>
+        <v>105.8436217308044</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9974229884587255</v>
+        <v>0.9555987839182706</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9971987634537949</v>
+        <v>0.9572399750110738</v>
       </c>
       <c r="G3" t="n">
-        <v>1.042999274810321</v>
+        <v>36.79692623075351</v>
       </c>
       <c r="H3" t="n">
-        <v>0.634718037848133</v>
+        <v>22.72192192440616</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4317066669464111</v>
+        <v>75.22472238540649</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9962821294270688</v>
+        <v>0.9516741927489486</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9978246390639918</v>
+        <v>0.9579448551240813</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9191254197681974</v>
+        <v>36.49237538596583</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6382677938619158</v>
+        <v>22.45833191275022</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 5, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8725149631500244</v>
+        <v>105.8436217308044</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9974229884587255</v>
+        <v>0.9555987839182706</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9971987634537949</v>
+        <v>0.9572399750110738</v>
       </c>
       <c r="G3" t="n">
-        <v>1.042999274810321</v>
+        <v>36.79692623075351</v>
       </c>
       <c r="H3" t="n">
-        <v>0.634718037848133</v>
+        <v>22.72192192440616</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>75.22472238540649</v>
+        <v>5.46375560760498</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9516741927489486</v>
+        <v>0.4348747454254791</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9579448551240813</v>
+        <v>0.5068453595120126</v>
       </c>
       <c r="G2" t="n">
-        <v>36.49237538596583</v>
+        <v>0.618008916640357</v>
       </c>
       <c r="H2" t="n">
-        <v>22.45833191275022</v>
+        <v>0.4624842125736865</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>105.8436217308044</v>
+        <v>9.000943183898926</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9555987839182706</v>
+        <v>0.4664842237832341</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9572399750110738</v>
+        <v>0.5068453595120126</v>
       </c>
       <c r="G3" t="n">
-        <v>36.79692623075351</v>
+        <v>0.618008916640357</v>
       </c>
       <c r="H3" t="n">
-        <v>22.72192192440616</v>
+        <v>0.4624842125736865</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>75.22472238540649</v>
+        <v>5.46375560760498</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9516741927489486</v>
+        <v>0.4348747454254791</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9579448551240813</v>
+        <v>0.5068453595120126</v>
       </c>
       <c r="G2" t="n">
-        <v>36.49237538596583</v>
+        <v>0.618008916640357</v>
       </c>
       <c r="H2" t="n">
-        <v>22.45833191275022</v>
+        <v>0.4624842125736865</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>105.8436217308044</v>
+        <v>9.000943183898926</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9555987839182706</v>
+        <v>0.4664842237832341</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9572399750110738</v>
+        <v>0.5068453595120126</v>
       </c>
       <c r="G3" t="n">
-        <v>36.79692623075351</v>
+        <v>0.618008916640357</v>
       </c>
       <c r="H3" t="n">
-        <v>22.72192192440616</v>
+        <v>0.4624842125736865</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.46375560760498</v>
+        <v>67.27135539054871</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4348747454254791</v>
+        <v>0.4401797218112232</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5068453595120126</v>
+        <v>0.4974964768614818</v>
       </c>
       <c r="G2" t="n">
-        <v>0.618008916640357</v>
+        <v>70.91261193281821</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4624842125736865</v>
+        <v>35.09659729829767</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>9.000943183898926</v>
+        <v>104.5934495925903</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4664842237832341</v>
+        <v>0.4797057452240424</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5068453595120126</v>
+        <v>0.4974964768614818</v>
       </c>
       <c r="G3" t="n">
-        <v>0.618008916640357</v>
+        <v>70.91261193281821</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4624842125736865</v>
+        <v>35.09659729829767</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.46375560760498</v>
+        <v>67.27135539054871</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4348747454254791</v>
+        <v>0.4401797218112232</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5068453595120126</v>
+        <v>0.4974964768614818</v>
       </c>
       <c r="G2" t="n">
-        <v>0.618008916640357</v>
+        <v>70.91261193281821</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4624842125736865</v>
+        <v>35.09659729829767</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>9.000943183898926</v>
+        <v>104.5934495925903</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4664842237832341</v>
+        <v>0.4797057452240424</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5068453595120126</v>
+        <v>0.4974964768614818</v>
       </c>
       <c r="G3" t="n">
-        <v>0.618008916640357</v>
+        <v>70.91261193281821</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4624842125736865</v>
+        <v>35.09659729829767</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>67.27135539054871</v>
+        <v>0.7079942226409912</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4401797218112232</v>
+        <v>0.9962821294270688</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4974964768614818</v>
+        <v>0.9978246390639918</v>
       </c>
       <c r="G2" t="n">
-        <v>70.91261193281821</v>
+        <v>0.9191254197681974</v>
       </c>
       <c r="H2" t="n">
-        <v>35.09659729829767</v>
+        <v>0.6382677938619158</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>104.5934495925903</v>
+        <v>1.160781383514404</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4797057452240424</v>
+        <v>0.9974229884587255</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4974964768614818</v>
+        <v>0.9971987634537949</v>
       </c>
       <c r="G3" t="n">
-        <v>70.91261193281821</v>
+        <v>1.042999274810321</v>
       </c>
       <c r="H3" t="n">
-        <v>35.09659729829767</v>
+        <v>0.634718037848133</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.040958404541016</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9978558588089712</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9971987634537949</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.042999274810321</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.634718037848133</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>67.27135539054871</v>
+        <v>0.7079942226409912</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4401797218112232</v>
+        <v>0.9962821294270688</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4974964768614818</v>
+        <v>0.9978246390639918</v>
       </c>
       <c r="G2" t="n">
-        <v>70.91261193281821</v>
+        <v>0.9191254197681974</v>
       </c>
       <c r="H2" t="n">
-        <v>35.09659729829767</v>
+        <v>0.6382677938619158</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>104.5934495925903</v>
+        <v>1.160781383514404</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4797057452240424</v>
+        <v>0.9974229884587255</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4974964768614818</v>
+        <v>0.9971987634537949</v>
       </c>
       <c r="G3" t="n">
-        <v>70.91261193281821</v>
+        <v>1.042999274810321</v>
       </c>
       <c r="H3" t="n">
-        <v>35.09659729829767</v>
+        <v>0.634718037848133</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.040958404541016</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9978558588089712</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9971987634537949</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.042999274810321</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.634718037848133</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7079942226409912</v>
+        <v>14.13356161117554</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9962821294270688</v>
+        <v>0.9516741927489486</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9978246390639918</v>
+        <v>0.9579448551240813</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9191254197681974</v>
+        <v>36.49237538596583</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6382677938619158</v>
+        <v>22.45833191275022</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 5, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.160781383514404</v>
+        <v>27.21209073066711</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9974229884587255</v>
+        <v>0.9555987839182706</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9971987634537949</v>
+        <v>0.9572399750110738</v>
       </c>
       <c r="G3" t="n">
-        <v>1.042999274810321</v>
+        <v>36.79692623075351</v>
       </c>
       <c r="H3" t="n">
-        <v>0.634718037848133</v>
+        <v>22.72192192440616</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>GradientBoosting</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.040958404541016</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9978558588089712</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9971987634537949</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.042999274810321</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.634718037848133</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7079942226409912</v>
+        <v>14.13356161117554</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9962821294270688</v>
+        <v>0.9516741927489486</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9978246390639918</v>
+        <v>0.9579448551240813</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9191254197681974</v>
+        <v>36.49237538596583</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6382677938619158</v>
+        <v>22.45833191275022</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 5, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.160781383514404</v>
+        <v>27.21209073066711</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9974229884587255</v>
+        <v>0.9555987839182706</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9971987634537949</v>
+        <v>0.9572399750110738</v>
       </c>
       <c r="G3" t="n">
-        <v>1.042999274810321</v>
+        <v>36.79692623075351</v>
       </c>
       <c r="H3" t="n">
-        <v>0.634718037848133</v>
+        <v>22.72192192440616</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>GradientBoosting</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.040958404541016</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9978558588089712</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9971987634537949</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.042999274810321</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.634718037848133</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>14.13356161117554</v>
+        <v>68.56809163093567</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9516741927489486</v>
+        <v>0.9999509803336641</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9579448551240813</v>
+        <v>0.9999639062073347</v>
       </c>
       <c r="G2" t="n">
-        <v>36.49237538596583</v>
+        <v>0.05767475851971326</v>
       </c>
       <c r="H2" t="n">
-        <v>22.45833191275022</v>
+        <v>0.02854199958467986</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>27.21209073066711</v>
+        <v>131.5601994991302</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9555987839182706</v>
+        <v>0.9999587994980429</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9572399750110738</v>
+        <v>0.9999686703599214</v>
       </c>
       <c r="G3" t="n">
-        <v>36.79692623075351</v>
+        <v>0.05373375960316539</v>
       </c>
       <c r="H3" t="n">
-        <v>22.72192192440616</v>
+        <v>0.02588015723046504</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>14.13356161117554</v>
+        <v>68.56809163093567</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9516741927489486</v>
+        <v>0.9999509803336641</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9579448551240813</v>
+        <v>0.9999639062073347</v>
       </c>
       <c r="G2" t="n">
-        <v>36.49237538596583</v>
+        <v>0.05767475851971326</v>
       </c>
       <c r="H2" t="n">
-        <v>22.45833191275022</v>
+        <v>0.02854199958467986</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>27.21209073066711</v>
+        <v>131.5601994991302</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9555987839182706</v>
+        <v>0.9999587994980429</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9572399750110738</v>
+        <v>0.9999686703599214</v>
       </c>
       <c r="G3" t="n">
-        <v>36.79692623075351</v>
+        <v>0.05373375960316539</v>
       </c>
       <c r="H3" t="n">
-        <v>22.72192192440616</v>
+        <v>0.02588015723046504</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>68.56809163093567</v>
+        <v>67.05084180831909</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999509803336641</v>
+        <v>0.4401797218112232</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999639062073347</v>
+        <v>0.4974964768614818</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05767475851971326</v>
+        <v>70.91261193281821</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02854199958467986</v>
+        <v>35.09659729829767</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
         </is>
       </c>
     </row>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>131.5601994991302</v>
+        <v>104.0239977836609</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999587994980429</v>
+        <v>0.4797057452240424</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999686703599214</v>
+        <v>0.4974964768614818</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05373375960316539</v>
+        <v>70.91261193281821</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02588015723046504</v>
+        <v>35.09659729829767</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>68.56809163093567</v>
+        <v>67.05084180831909</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999509803336641</v>
+        <v>0.4401797218112232</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999639062073347</v>
+        <v>0.4974964768614818</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05767475851971326</v>
+        <v>70.91261193281821</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02854199958467986</v>
+        <v>35.09659729829767</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
         </is>
       </c>
     </row>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>131.5601994991302</v>
+        <v>104.0239977836609</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999587994980429</v>
+        <v>0.4797057452240424</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999686703599214</v>
+        <v>0.4974964768614818</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05373375960316539</v>
+        <v>70.91261193281821</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02588015723046504</v>
+        <v>35.09659729829767</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>67.05084180831909</v>
+        <v>212.3113346099854</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4401797218112232</v>
+        <v>0.9086459277482887</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4974964768614818</v>
+        <v>0.9234507192447867</v>
       </c>
       <c r="G2" t="n">
-        <v>70.91261193281821</v>
+        <v>9.386926059133257</v>
       </c>
       <c r="H2" t="n">
-        <v>35.09659729829767</v>
+        <v>5.775696783249589</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>104.0239977836609</v>
+        <v>366.6692905426025</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4797057452240424</v>
+        <v>0.9128931506703857</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4974964768614818</v>
+        <v>0.9234507192447867</v>
       </c>
       <c r="G3" t="n">
-        <v>70.91261193281821</v>
+        <v>9.386926059133257</v>
       </c>
       <c r="H3" t="n">
-        <v>35.09659729829767</v>
+        <v>5.775696783249589</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>67.05084180831909</v>
+        <v>212.3113346099854</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4401797218112232</v>
+        <v>0.9086459277482887</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4974964768614818</v>
+        <v>0.9234507192447867</v>
       </c>
       <c r="G2" t="n">
-        <v>70.91261193281821</v>
+        <v>9.386926059133257</v>
       </c>
       <c r="H2" t="n">
-        <v>35.09659729829767</v>
+        <v>5.775696783249589</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>104.0239977836609</v>
+        <v>366.6692905426025</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4797057452240424</v>
+        <v>0.9128931506703857</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4974964768614818</v>
+        <v>0.9234507192447867</v>
       </c>
       <c r="G3" t="n">
-        <v>70.91261193281821</v>
+        <v>9.386926059133257</v>
       </c>
       <c r="H3" t="n">
-        <v>35.09659729829767</v>
+        <v>5.775696783249589</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>212.3113346099854</v>
+        <v>37.40417456626892</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9086459277482887</v>
+        <v>0.440750682226018</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9234507192447867</v>
+        <v>0.5417900273946938</v>
       </c>
       <c r="G2" t="n">
-        <v>9.386926059133257</v>
+        <v>0.5957107641453661</v>
       </c>
       <c r="H2" t="n">
-        <v>5.775696783249589</v>
+        <v>0.4244218364523328</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>366.6692905426025</v>
+        <v>70.7239203453064</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9128931506703857</v>
+        <v>0.4777373636797072</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9234507192447867</v>
+        <v>0.5291968951379508</v>
       </c>
       <c r="G3" t="n">
-        <v>9.386926059133257</v>
+        <v>0.603841334418266</v>
       </c>
       <c r="H3" t="n">
-        <v>5.775696783249589</v>
+        <v>0.4316743421594985</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_samples_split': 10, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>212.3113346099854</v>
+        <v>37.40417456626892</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9086459277482887</v>
+        <v>0.440750682226018</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9234507192447867</v>
+        <v>0.5417900273946938</v>
       </c>
       <c r="G2" t="n">
-        <v>9.386926059133257</v>
+        <v>0.5957107641453661</v>
       </c>
       <c r="H2" t="n">
-        <v>5.775696783249589</v>
+        <v>0.4244218364523328</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>366.6692905426025</v>
+        <v>70.7239203453064</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9128931506703857</v>
+        <v>0.4777373636797072</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9234507192447867</v>
+        <v>0.5291968951379508</v>
       </c>
       <c r="G3" t="n">
-        <v>9.386926059133257</v>
+        <v>0.603841334418266</v>
       </c>
       <c r="H3" t="n">
-        <v>5.775696783249589</v>
+        <v>0.4316743421594985</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_samples_split': 10, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>37.40417456626892</v>
+        <v>0.6025295257568359</v>
       </c>
       <c r="E2" t="n">
-        <v>0.440750682226018</v>
+        <v>0.9962821294270688</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5417900273946938</v>
+        <v>0.9978246390639918</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5957107641453661</v>
+        <v>0.9191254197681974</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4244218364523328</v>
+        <v>0.6382677938619158</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>70.7239203453064</v>
+        <v>1.168087482452393</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4777373636797072</v>
+        <v>0.9974229884587255</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5291968951379508</v>
+        <v>0.9971987634537949</v>
       </c>
       <c r="G3" t="n">
-        <v>0.603841334418266</v>
+        <v>1.042999274810321</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4316743421594985</v>
+        <v>0.634718037848133</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_samples_split': 10, 'n_estimators': 200}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.963010787963867</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9978558588089712</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9971987634537949</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.042999274810321</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.634718037848133</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>37.40417456626892</v>
+        <v>0.6025295257568359</v>
       </c>
       <c r="E2" t="n">
-        <v>0.440750682226018</v>
+        <v>0.9962821294270688</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5417900273946938</v>
+        <v>0.9978246390639918</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5957107641453661</v>
+        <v>0.9191254197681974</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4244218364523328</v>
+        <v>0.6382677938619158</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>70.7239203453064</v>
+        <v>1.168087482452393</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4777373636797072</v>
+        <v>0.9974229884587255</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5291968951379508</v>
+        <v>0.9971987634537949</v>
       </c>
       <c r="G3" t="n">
-        <v>0.603841334418266</v>
+        <v>1.042999274810321</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4316743421594985</v>
+        <v>0.634718037848133</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_samples_split': 10, 'n_estimators': 200}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.963010787963867</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9978558588089712</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9971987634537949</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.042999274810321</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.634718037848133</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6025295257568359</v>
+        <v>0.8413887023925781</v>
       </c>
       <c r="E2" t="n">
         <v>0.9962821294270688</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.168087482452393</v>
+        <v>1.500933647155762</v>
       </c>
       <c r="E3" t="n">
         <v>0.9974229884587255</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.963010787963867</v>
+        <v>3.030790567398071</v>
       </c>
       <c r="E4" t="n">
         <v>0.9978558588089712</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6025295257568359</v>
+        <v>0.8413887023925781</v>
       </c>
       <c r="E2" t="n">
         <v>0.9962821294270688</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.168087482452393</v>
+        <v>1.500933647155762</v>
       </c>
       <c r="E3" t="n">
         <v>0.9974229884587255</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.963010787963867</v>
+        <v>3.030790567398071</v>
       </c>
       <c r="E4" t="n">
         <v>0.9978558588089712</v>

--- a/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8413887023925781</v>
+        <v>23.98345422744751</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9962821294270688</v>
+        <v>0.9358564357913293</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9978246390639918</v>
+        <v>0.9335005210846987</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9191254197681974</v>
+        <v>34.39282212503215</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6382677938619158</v>
+        <v>20.89310493392084</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 5, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -523,61 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>1.500933647155762</v>
+        <v>47.19415616989136</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9974229884587255</v>
+        <v>0.9371377236464621</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9971987634537949</v>
+        <v>0.9335005210846987</v>
       </c>
       <c r="G3" t="n">
-        <v>1.042999274810321</v>
+        <v>34.39282212503215</v>
       </c>
       <c r="H3" t="n">
-        <v>0.634718037848133</v>
+        <v>20.89310493392084</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>GradientBoosting</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3.030790567398071</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9978558588089712</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9971987634537949</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.042999274810321</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.634718037848133</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8413887023925781</v>
+        <v>23.98345422744751</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9962821294270688</v>
+        <v>0.9358564357913293</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9978246390639918</v>
+        <v>0.9335005210846987</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9191254197681974</v>
+        <v>34.39282212503215</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6382677938619158</v>
+        <v>20.89310493392084</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 5, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -689,61 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>1.500933647155762</v>
+        <v>47.19415616989136</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9974229884587255</v>
+        <v>0.9371377236464621</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9971987634537949</v>
+        <v>0.9335005210846987</v>
       </c>
       <c r="G3" t="n">
-        <v>1.042999274810321</v>
+        <v>34.39282212503215</v>
       </c>
       <c r="H3" t="n">
-        <v>0.634718037848133</v>
+        <v>20.89310493392084</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>GradientBoosting</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3.030790567398071</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9978558588089712</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9971987634537949</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.042999274810321</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.634718037848133</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>23.98345422744751</v>
+        <v>1.208387851715088</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9358564357913293</v>
+        <v>0.9962821294270688</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9335005210846987</v>
+        <v>0.9978246390639918</v>
       </c>
       <c r="G2" t="n">
-        <v>34.39282212503215</v>
+        <v>0.9191254197681974</v>
       </c>
       <c r="H2" t="n">
-        <v>20.89310493392084</v>
+        <v>0.6382677938619158</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -523,26 +523,61 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>47.19415616989136</v>
+        <v>2.340327739715576</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9371377236464621</v>
+        <v>0.9974229884587255</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9335005210846987</v>
+        <v>0.9971987634537949</v>
       </c>
       <c r="G3" t="n">
-        <v>34.39282212503215</v>
+        <v>1.042999274810321</v>
       </c>
       <c r="H3" t="n">
-        <v>20.89310493392084</v>
+        <v>0.634718037848133</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.603539228439331</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9978558588089712</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9971987634537949</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.042999274810321</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.634718037848133</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,26 +654,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>23.98345422744751</v>
+        <v>1.208387851715088</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9358564357913293</v>
+        <v>0.9962821294270688</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9335005210846987</v>
+        <v>0.9978246390639918</v>
       </c>
       <c r="G2" t="n">
-        <v>34.39282212503215</v>
+        <v>0.9191254197681974</v>
       </c>
       <c r="H2" t="n">
-        <v>20.89310493392084</v>
+        <v>0.6382677938619158</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -654,26 +689,61 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>47.19415616989136</v>
+        <v>2.340327739715576</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9371377236464621</v>
+        <v>0.9974229884587255</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9335005210846987</v>
+        <v>0.9971987634537949</v>
       </c>
       <c r="G3" t="n">
-        <v>34.39282212503215</v>
+        <v>1.042999274810321</v>
       </c>
       <c r="H3" t="n">
-        <v>20.89310493392084</v>
+        <v>0.634718037848133</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.603539228439331</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9978558588089712</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9971987634537949</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.042999274810321</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.634718037848133</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.208387851715088</v>
+        <v>111.7759871482849</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9962821294270688</v>
+        <v>0.9999596685562091</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9978246390639918</v>
+        <v>0.9999751355245586</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9191254197681974</v>
+        <v>0.04728616597242019</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6382677938619158</v>
+        <v>0.0236837833684335</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 5, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.340327739715576</v>
+        <v>193.0010094642639</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9974229884587255</v>
+        <v>0.9999660970286026</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9971987634537949</v>
+        <v>0.9999751355245586</v>
       </c>
       <c r="G3" t="n">
-        <v>1.042999274810321</v>
+        <v>0.04728616597242019</v>
       </c>
       <c r="H3" t="n">
-        <v>0.634718037848133</v>
+        <v>0.0236837833684335</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>GradientBoosting</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4.603539228439331</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9978558588089712</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9971987634537949</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.042999274810321</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.634718037848133</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.208387851715088</v>
+        <v>111.7759871482849</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9962821294270688</v>
+        <v>0.9999596685562091</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9978246390639918</v>
+        <v>0.9999751355245586</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9191254197681974</v>
+        <v>0.04728616597242019</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6382677938619158</v>
+        <v>0.0236837833684335</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 5, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.340327739715576</v>
+        <v>193.0010094642639</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9974229884587255</v>
+        <v>0.9999660970286026</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9971987634537949</v>
+        <v>0.9999751355245586</v>
       </c>
       <c r="G3" t="n">
-        <v>1.042999274810321</v>
+        <v>0.04728616597242019</v>
       </c>
       <c r="H3" t="n">
-        <v>0.634718037848133</v>
+        <v>0.0236837833684335</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>GradientBoosting</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4.603539228439331</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9978558588089712</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9971987634537949</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.042999274810321</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.634718037848133</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_GradientBoosting_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>111.7759871482849</v>
+        <v>108.4727911949158</v>
       </c>
       <c r="E2" t="n">
         <v>0.9999596685562091</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>193.0010094642639</v>
+        <v>178.9059579372406</v>
       </c>
       <c r="E3" t="n">
         <v>0.9999660970286026</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>111.7759871482849</v>
+        <v>108.4727911949158</v>
       </c>
       <c r="E2" t="n">
         <v>0.9999596685562091</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>193.0010094642639</v>
+        <v>178.9059579372406</v>
       </c>
       <c r="E3" t="n">
         <v>0.9999660970286026</v>
